--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t>据点</t>
+  </si>
+  <si>
+    <t>Main_Home</t>
   </si>
   <si>
     <t>新手村</t>
@@ -1147,7 +1150,9 @@
       <c r="D5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
@@ -1157,13 +1162,13 @@
         <v>100</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" t="b">
@@ -1175,13 +1180,13 @@
         <v>101</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" t="b">

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -55,9 +55,6 @@
     <t>##type</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
@@ -88,25 +85,40 @@
     <t>警戒标记</t>
   </si>
   <si>
+    <t>base_01</t>
+  </si>
+  <si>
     <t>据点</t>
   </si>
   <si>
     <t>Main_Home</t>
   </si>
   <si>
-    <t>新手村</t>
-  </si>
-  <si>
-    <t>出门第一张地图</t>
+    <t>village_01</t>
+  </si>
+  <si>
+    <t>村子1</t>
+  </si>
+  <si>
+    <t>村子2</t>
   </si>
   <si>
     <t>Main_Area_01</t>
   </si>
   <si>
-    <t>村子2</t>
+    <t>village_02</t>
   </si>
   <si>
     <t>Main_Area_02</t>
+  </si>
+  <si>
+    <t>game_init</t>
+  </si>
+  <si>
+    <t>出生点</t>
+  </si>
+  <si>
+    <t>Main_Init</t>
   </si>
 </sst>
 </file>
@@ -1040,9 +1052,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
+    <col min="2" max="2" width="19" customWidth="1"/>
     <col min="4" max="4" width="16.125" customWidth="1"/>
     <col min="5" max="6" width="21" customWidth="1"/>
     <col min="7" max="7" width="28.25" customWidth="1"/>
@@ -1080,69 +1093,69 @@
         <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="G2" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1"/>
-      <c r="B5" s="1">
-        <v>1</v>
+      <c r="B5" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>19</v>
@@ -1158,40 +1171,54 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="B6" s="1">
-        <v>100</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="C6" t="s">
         <v>22</v>
       </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="1"/>
+        <v>24</v>
+      </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="B7" s="1">
-        <v>101</v>
+      <c r="B7" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" t="b">
         <v>1</v>
       </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -52,6 +52,9 @@
     <t>always_alert</t>
   </si>
   <si>
+    <t>default_disguise</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -85,6 +88,9 @@
     <t>警戒标记</t>
   </si>
   <si>
+    <t>默认伪装</t>
+  </si>
+  <si>
     <t>base_01</t>
   </si>
   <si>
@@ -119,6 +125,15 @@
   </si>
   <si>
     <t>Main_Init</t>
+  </si>
+  <si>
+    <t>base_fight</t>
+  </si>
+  <si>
+    <t>纷争据点</t>
+  </si>
+  <si>
+    <t>Main_Home_Fight</t>
   </si>
 </sst>
 </file>
@@ -1052,8 +1067,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="4" max="4" width="16.125" customWidth="1"/>
@@ -1062,7 +1077,7 @@
     <col min="8" max="8" width="23.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1084,141 +1099,179 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" t="b">
         <v>1</v>
       </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F9" s="1"/>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -1,307 +1,182 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="area_info" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="area_info" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="world_map_area" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="world_map_room_rule" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="world_map_settings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>scene_name</t>
-  </si>
-  <si>
-    <t>is_home</t>
-  </si>
-  <si>
-    <t>always_alert</t>
-  </si>
-  <si>
-    <t>default_disguise</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c,s</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>场景名</t>
-  </si>
-  <si>
-    <t>警戒标记</t>
-  </si>
-  <si>
-    <t>默认伪装</t>
-  </si>
-  <si>
-    <t>base_01</t>
-  </si>
-  <si>
-    <t>据点</t>
-  </si>
-  <si>
-    <t>Main_Home</t>
-  </si>
-  <si>
-    <t>village_01</t>
-  </si>
-  <si>
-    <t>村子1</t>
-  </si>
-  <si>
-    <t>村子2</t>
-  </si>
-  <si>
-    <t>Main_Area_01</t>
-  </si>
-  <si>
-    <t>village_02</t>
-  </si>
-  <si>
-    <t>Main_Area_02</t>
-  </si>
-  <si>
-    <t>game_init</t>
-  </si>
-  <si>
-    <t>出生点</t>
-  </si>
-  <si>
-    <t>Main_Init</t>
-  </si>
-  <si>
-    <t>base_fight</t>
-  </si>
-  <si>
-    <t>纷争据点</t>
-  </si>
-  <si>
-    <t>Main_Home_Fight</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -601,161 +476,162 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -809,11 +685,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1065,241 +1004,1032 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="4" max="4" width="16.125" customWidth="1"/>
-    <col min="5" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="28.25" customWidth="1"/>
-    <col min="8" max="8" width="23.625" customWidth="1"/>
+    <col width="19" customWidth="1" style="2" min="2" max="2"/>
+    <col width="16.125" customWidth="1" style="2" min="4" max="4"/>
+    <col width="21" customWidth="1" style="2" min="5" max="6"/>
+    <col width="28.25" customWidth="1" style="2" min="7" max="7"/>
+    <col width="23.625" customWidth="1" style="2" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>scene_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>is_home</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>always_alert</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>default_disguise</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>场景名</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>警戒标记</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>警戒标记</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>默认伪装</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>base_01</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>据点</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>据点</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Main_Home</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="6">
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>village_01</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>村子1</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>村子2</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Main_Area_01</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" t="b">
+      <c r="H6" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="B6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" t="b">
+    <row r="7">
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>village_02</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>村子2</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>村子2</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Main_Area_02</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="n"/>
+      <c r="G7" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="H6" t="b">
+      <c r="H7" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="B7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" t="b">
+    <row r="9">
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>game_init</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>出生点</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>出生点</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>Main_Init</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="n"/>
+      <c r="G9" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="B9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" t="b">
+    </row>
+    <row r="10">
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>base_fight</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>纷争据点</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>纷争据点</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Main_Home_Fight</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>map_texture_resource_path</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>world_min_x</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>world_min_y</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>world_max_x</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>world_max_y</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>区域 id（与 MapAreaInfo.id / MapName 一致）</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Resources 路径无扩展名</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>base_01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>WorldMap/fake_map_base_01</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-50</v>
+      </c>
+      <c r="F5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>village_01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>WorldMap/fake_map_village_01</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-50</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-50</v>
+      </c>
+      <c r="F6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>game_init</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>WorldMap/fake_map_game_init</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-50</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-50</v>
+      </c>
+      <c r="F7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>area_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>room_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>rule_priority</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>behavior</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>alternate_map_texture_resource_path</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>use_separate_bounds</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>alternate_world_min_x</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>alternate_world_min_y</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>alternate_world_max_x</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>alternate_world_max_y</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>EWorldMapRoomBehavior</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>规则 id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>所属区域</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>房间 id，* 为默认</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>同区多条时大者优先</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>行为</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>换图时纹理路径</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>是否用独立边界</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>alt min/max</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>allow_open_when_area_unknown</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fallback_map_texture_resource_path</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fallback_world_min_x</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fallback_world_min_y</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>fallback_world_max_x</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>fallback_world_max_y</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>global_npc_boss_landmark_cfg_ids</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>global_interact_landmark_cfg_ids</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>未知区域是否允许打开</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>fallback 纹理 Resources 路径</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fallback 边界</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>逗号分隔 cfgId</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>逗号分隔 cfgId</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>WorldMap/fake_map_fallback</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-40</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-40</v>
+      </c>
+      <c r="F5" t="n">
+        <v>40</v>
+      </c>
+      <c r="G5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="area_info" sheetId="1" r:id="rId1"/>
@@ -1544,6 +1544,10 @@
   <sheetPr/>
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <cols>
+    <col min="3" max="3" width="17.375" customWidth="1"/>
+    <col min="8" max="8" width="33.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="2"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="area_info" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="77">
   <si>
     <t>##var</t>
   </si>
@@ -55,6 +55,12 @@
     <t>default_disguise</t>
   </si>
   <si>
+    <t>hunting_target</t>
+  </si>
+  <si>
+    <t>hunting_unlock_conds</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -64,6 +70,9 @@
     <t>bool</t>
   </si>
   <si>
+    <t>(list#sep=;),CommonCheckCond</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -89,6 +98,12 @@
   </si>
   <si>
     <t>默认伪装</t>
+  </si>
+  <si>
+    <t>是否是出击目标</t>
+  </si>
+  <si>
+    <t>解锁条件</t>
   </si>
   <si>
     <t>base_01</t>
@@ -1176,17 +1191,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.125" style="1" customWidth="1"/>
     <col min="5" max="6" width="21" style="1" customWidth="1"/>
     <col min="7" max="7" width="28.25" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5" customWidth="1"/>
+    <col min="10" max="10" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1211,112 +1228,136 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>12</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>15</v>
+      </c>
+      <c r="I3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="B5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:10">
       <c r="B6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -1324,19 +1365,22 @@
       <c r="H6" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="B7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F7"/>
       <c r="G7" t="b">
@@ -1345,37 +1389,40 @@
       <c r="H7" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F9"/>
       <c r="G9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:10">
       <c r="B10" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -1399,112 +1446,112 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1512,7 +1559,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D5">
         <v>-40</v>
@@ -1527,10 +1574,10 @@
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1557,145 +1604,145 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="J1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="L1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="L4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1703,13 +1750,13 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1718,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I5">
         <v>-50</v>
@@ -1738,13 +1785,13 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1753,7 +1800,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I6">
         <v>-50</v>
@@ -1773,13 +1820,13 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1788,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I7">
         <v>-50</v>

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="79">
   <si>
     <t>##var</t>
   </si>
@@ -52,7 +52,10 @@
     <t>always_alert</t>
   </si>
   <si>
-    <t>default_disguise</t>
+    <t>is_civil_area</t>
+  </si>
+  <si>
+    <t>is_danger_area</t>
   </si>
   <si>
     <t>hunting_target</t>
@@ -97,7 +100,12 @@
     <t>警戒标记</t>
   </si>
   <si>
-    <t>默认伪装</t>
+    <t>是否为文明区域
+城镇地带默认进行伪装</t>
+  </si>
+  <si>
+    <t>是否为危险区域
+危险区域无法以人形前往</t>
   </si>
   <si>
     <t>是否是出击目标</t>
@@ -875,11 +883,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1191,19 +1202,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.125" style="1" customWidth="1"/>
     <col min="5" max="6" width="21" style="1" customWidth="1"/>
     <col min="7" max="7" width="28.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="23.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5" customWidth="1"/>
-    <col min="10" max="10" width="12.75" customWidth="1"/>
+    <col min="8" max="9" width="23.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5" customWidth="1"/>
+    <col min="11" max="11" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1234,130 +1245,142 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
         <v>16</v>
       </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="27" spans="1:11">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" t="s">
         <v>22</v>
       </c>
-      <c r="I4" t="s">
+      <c r="H4" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="I4" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="J4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>25</v>
+      </c>
+      <c r="K4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="B5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="B6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -1365,22 +1388,23 @@
       <c r="H6" t="b">
         <v>1</v>
       </c>
-      <c r="I6" t="b">
+      <c r="I6"/>
+      <c r="J6" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F7"/>
       <c r="G7" t="b">
@@ -1389,40 +1413,41 @@
       <c r="H7" t="b">
         <v>1</v>
       </c>
-      <c r="I7" t="b">
+      <c r="I7"/>
+      <c r="J7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:11">
       <c r="B9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F9"/>
       <c r="G9" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:11">
       <c r="B10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -1446,112 +1471,112 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1559,7 +1584,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D5">
         <v>-40</v>
@@ -1574,10 +1599,10 @@
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1604,145 +1629,145 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
       <c r="I2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1750,13 +1775,13 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1765,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I5">
         <v>-50</v>
@@ -1785,13 +1810,13 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1800,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I6">
         <v>-50</v>
@@ -1820,13 +1845,13 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1835,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I7">
         <v>-50</v>

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="area_info" sheetId="1" r:id="rId1"/>
-    <sheet name="world_map_global" sheetId="4" r:id="rId2"/>
-    <sheet name="world_map_big_map" sheetId="5" r:id="rId3"/>
+    <sheet name="area_entry_info" sheetId="6" r:id="rId2"/>
+    <sheet name="world_map_global" sheetId="4" r:id="rId3"/>
+    <sheet name="world_map_big_map" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="85">
   <si>
     <t>##var</t>
   </si>
@@ -95,6 +96,9 @@
   </si>
   <si>
     <t>场景名</t>
+  </si>
+  <si>
+    <t>home标记</t>
   </si>
   <si>
     <t>警戒标记</t>
@@ -129,15 +133,15 @@
     <t>村子1</t>
   </si>
   <si>
+    <t>Main_Area_01</t>
+  </si>
+  <si>
+    <t>village_02</t>
+  </si>
+  <si>
     <t>村子2</t>
   </si>
   <si>
-    <t>Main_Area_01</t>
-  </si>
-  <si>
-    <t>village_02</t>
-  </si>
-  <si>
     <t>Main_Area_02</t>
   </si>
   <si>
@@ -159,6 +163,30 @@
     <t>Main_Home_Fight</t>
   </si>
   <si>
+    <t>map_id</t>
+  </si>
+  <si>
+    <t>day_period</t>
+  </si>
+  <si>
+    <t>dynamic_info_name</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>map名</t>
+  </si>
+  <si>
+    <t>昼夜信息
+0 无所谓
+1 白天
+2夜晚</t>
+  </si>
+  <si>
+    <t>动态配置文件</t>
+  </si>
+  <si>
     <t>allow_open_when_area_unknown</t>
   </si>
   <si>
@@ -204,9 +232,6 @@
     <t>WorldMap/fake_map_fallback</t>
   </si>
   <si>
-    <t>map_id</t>
-  </si>
-  <si>
     <t>region_key</t>
   </si>
   <si>
@@ -232,9 +257,6 @@
   </si>
   <si>
     <t>world_max_y</t>
-  </si>
-  <si>
-    <t>int</t>
   </si>
   <si>
     <t>主键</t>
@@ -887,10 +909,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1205,11 +1227,12 @@
   <dimension ref="A1:K10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="19" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="21" style="1" customWidth="1"/>
-    <col min="7" max="7" width="28.25" style="1" customWidth="1"/>
-    <col min="8" max="9" width="23.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.5" customWidth="1"/>
+    <col min="4" max="4" width="16.125" style="2" customWidth="1"/>
+    <col min="5" max="6" width="21" style="2" customWidth="1"/>
+    <col min="7" max="7" width="28.25" style="2" customWidth="1"/>
+    <col min="8" max="9" width="23.625" style="2" customWidth="1"/>
     <col min="10" max="10" width="15.5" customWidth="1"/>
     <col min="11" max="11" width="12.75" customWidth="1"/>
   </cols>
@@ -1337,33 +1360,33 @@
         <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="I4" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="B5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -1371,10 +1394,10 @@
     </row>
     <row r="6" spans="1:11">
       <c r="B6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
@@ -1398,13 +1421,13 @@
         <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7"/>
       <c r="G7" t="b">
@@ -1420,16 +1443,16 @@
     </row>
     <row r="9" spans="1:11">
       <c r="B9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F9"/>
       <c r="G9" t="b">
@@ -1438,16 +1461,16 @@
     </row>
     <row r="10" spans="1:11">
       <c r="B10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -1463,15 +1486,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
+  <cols>
+    <col min="2" max="2" width="12.25" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="11.875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>43</v>
@@ -1482,128 +1510,81 @@
       <c r="E1" t="s">
         <v>45</v>
       </c>
-      <c r="F1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" t="s">
         <v>12</v>
       </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+    </row>
+    <row r="4" ht="54" spans="1:5">
       <c r="A4" t="s">
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" t="s">
-        <v>54</v>
-      </c>
-      <c r="H4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="B5" t="b">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>-40</v>
-      </c>
-      <c r="E5">
-        <v>-40</v>
-      </c>
-      <c r="F5">
-        <v>40</v>
-      </c>
-      <c r="G5">
-        <v>40</v>
-      </c>
-      <c r="H5" t="s">
-        <v>54</v>
-      </c>
-      <c r="I5" t="s">
-        <v>54</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1612,6 +1593,157 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="B5" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5">
+        <v>-40</v>
+      </c>
+      <c r="E5">
+        <v>-40</v>
+      </c>
+      <c r="F5">
+        <v>40</v>
+      </c>
+      <c r="G5">
+        <v>40</v>
+      </c>
+      <c r="H5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L7"/>
@@ -1629,34 +1761,34 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="I1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="K1" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="L1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1664,7 +1796,7 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
@@ -1676,7 +1808,7 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -1685,16 +1817,16 @@
         <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="J2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="L2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1737,37 +1869,37 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I4" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J4" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="K4" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="L4" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1775,13 +1907,13 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1790,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="I5">
         <v>-50</v>
@@ -1810,13 +1942,13 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1825,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I6">
         <v>-50</v>
@@ -1845,13 +1977,13 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1860,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I7">
         <v>-50</v>

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -4,13 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="area_info" sheetId="1" r:id="rId1"/>
-    <sheet name="area_entry_info" sheetId="6" r:id="rId2"/>
-    <sheet name="world_map_global" sheetId="4" r:id="rId3"/>
-    <sheet name="world_map_big_map" sheetId="5" r:id="rId4"/>
+    <sheet name="world_map_global" sheetId="4" r:id="rId2"/>
+    <sheet name="world_map_big_map" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="86">
   <si>
     <t>##var</t>
   </si>
@@ -44,9 +43,15 @@
     <t>desc</t>
   </si>
   <si>
+    <t>day_period_limit</t>
+  </si>
+  <si>
     <t>scene_name</t>
   </si>
   <si>
+    <t>map_data_name</t>
+  </si>
+  <si>
     <t>is_home</t>
   </si>
   <si>
@@ -71,6 +76,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>bool</t>
   </si>
   <si>
@@ -95,7 +103,13 @@
     <t>描述</t>
   </si>
   <si>
+    <t>时间要求</t>
+  </si>
+  <si>
     <t>场景名</t>
+  </si>
+  <si>
+    <t>数据文件名</t>
   </si>
   <si>
     <t>home标记</t>
@@ -127,163 +141,148 @@
     <t>Main_Home</t>
   </si>
   <si>
+    <t>village_01_d</t>
+  </si>
+  <si>
+    <t>村子1</t>
+  </si>
+  <si>
+    <t>Main_Area_01</t>
+  </si>
+  <si>
+    <t>village_01_n</t>
+  </si>
+  <si>
+    <t>village_02</t>
+  </si>
+  <si>
+    <t>村子2</t>
+  </si>
+  <si>
+    <t>Main_Area_02</t>
+  </si>
+  <si>
+    <t>game_init</t>
+  </si>
+  <si>
+    <t>出生点</t>
+  </si>
+  <si>
+    <t>Main_Init</t>
+  </si>
+  <si>
+    <t>base_fight</t>
+  </si>
+  <si>
+    <t>纷争据点</t>
+  </si>
+  <si>
+    <t>Main_Home_Fight</t>
+  </si>
+  <si>
+    <t>allow_open_when_area_unknown</t>
+  </si>
+  <si>
+    <t>fallback_big_map_texture_resource_path</t>
+  </si>
+  <si>
+    <t>fallback_world_min_x</t>
+  </si>
+  <si>
+    <t>fallback_world_min_y</t>
+  </si>
+  <si>
+    <t>fallback_world_max_x</t>
+  </si>
+  <si>
+    <t>fallback_world_max_y</t>
+  </si>
+  <si>
+    <t>global_npc_boss_landmark_cfg_ids</t>
+  </si>
+  <si>
+    <t>global_interact_landmark_cfg_ids</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>未知地图是否可开</t>
+  </si>
+  <si>
+    <t>fallback 底图</t>
+  </si>
+  <si>
+    <t>边界</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>逗号分隔</t>
+  </si>
+  <si>
+    <t>WorldMap/fake_map_fallback</t>
+  </si>
+  <si>
+    <t>map_id</t>
+  </si>
+  <si>
+    <t>region_key</t>
+  </si>
+  <si>
+    <t>room_id</t>
+  </si>
+  <si>
+    <t>rule_priority</t>
+  </si>
+  <si>
+    <t>forbid_open_world_map</t>
+  </si>
+  <si>
+    <t>big_map_texture_resource_path</t>
+  </si>
+  <si>
+    <t>world_min_x</t>
+  </si>
+  <si>
+    <t>world_min_y</t>
+  </si>
+  <si>
+    <t>world_max_x</t>
+  </si>
+  <si>
+    <t>world_max_y</t>
+  </si>
+  <si>
+    <t>主键</t>
+  </si>
+  <si>
+    <t>MapName</t>
+  </si>
+  <si>
+    <t>策划分区名</t>
+  </si>
+  <si>
+    <t>空/* 默认</t>
+  </si>
+  <si>
+    <t>大优先</t>
+  </si>
+  <si>
+    <t>禁止打开</t>
+  </si>
+  <si>
+    <t>底图路径</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>WorldMap/fake_map_base_01</t>
+  </si>
+  <si>
     <t>village_01</t>
-  </si>
-  <si>
-    <t>村子1</t>
-  </si>
-  <si>
-    <t>Main_Area_01</t>
-  </si>
-  <si>
-    <t>village_02</t>
-  </si>
-  <si>
-    <t>村子2</t>
-  </si>
-  <si>
-    <t>Main_Area_02</t>
-  </si>
-  <si>
-    <t>game_init</t>
-  </si>
-  <si>
-    <t>出生点</t>
-  </si>
-  <si>
-    <t>Main_Init</t>
-  </si>
-  <si>
-    <t>base_fight</t>
-  </si>
-  <si>
-    <t>纷争据点</t>
-  </si>
-  <si>
-    <t>Main_Home_Fight</t>
-  </si>
-  <si>
-    <t>map_id</t>
-  </si>
-  <si>
-    <t>day_period</t>
-  </si>
-  <si>
-    <t>dynamic_info_name</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>map名</t>
-  </si>
-  <si>
-    <t>昼夜信息
-0 无所谓
-1 白天
-2夜晚</t>
-  </si>
-  <si>
-    <t>动态配置文件</t>
-  </si>
-  <si>
-    <t>allow_open_when_area_unknown</t>
-  </si>
-  <si>
-    <t>fallback_big_map_texture_resource_path</t>
-  </si>
-  <si>
-    <t>fallback_world_min_x</t>
-  </si>
-  <si>
-    <t>fallback_world_min_y</t>
-  </si>
-  <si>
-    <t>fallback_world_max_x</t>
-  </si>
-  <si>
-    <t>fallback_world_max_y</t>
-  </si>
-  <si>
-    <t>global_npc_boss_landmark_cfg_ids</t>
-  </si>
-  <si>
-    <t>global_interact_landmark_cfg_ids</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>未知地图是否可开</t>
-  </si>
-  <si>
-    <t>fallback 底图</t>
-  </si>
-  <si>
-    <t>边界</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>逗号分隔</t>
-  </si>
-  <si>
-    <t>WorldMap/fake_map_fallback</t>
-  </si>
-  <si>
-    <t>region_key</t>
-  </si>
-  <si>
-    <t>room_id</t>
-  </si>
-  <si>
-    <t>rule_priority</t>
-  </si>
-  <si>
-    <t>forbid_open_world_map</t>
-  </si>
-  <si>
-    <t>big_map_texture_resource_path</t>
-  </si>
-  <si>
-    <t>world_min_x</t>
-  </si>
-  <si>
-    <t>world_min_y</t>
-  </si>
-  <si>
-    <t>world_max_x</t>
-  </si>
-  <si>
-    <t>world_max_y</t>
-  </si>
-  <si>
-    <t>主键</t>
-  </si>
-  <si>
-    <t>MapName</t>
-  </si>
-  <si>
-    <t>策划分区名</t>
-  </si>
-  <si>
-    <t>空/* 默认</t>
-  </si>
-  <si>
-    <t>大优先</t>
-  </si>
-  <si>
-    <t>禁止打开</t>
-  </si>
-  <si>
-    <t>底图路径</t>
-  </si>
-  <si>
-    <t>default</t>
-  </si>
-  <si>
-    <t>WorldMap/fake_map_base_01</t>
   </si>
   <si>
     <t>WorldMap/fake_map_village_01</t>
@@ -909,10 +908,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1224,20 +1223,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="19.25" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.25" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.5" customWidth="1"/>
-    <col min="4" max="4" width="16.125" style="2" customWidth="1"/>
-    <col min="5" max="6" width="21" style="2" customWidth="1"/>
-    <col min="7" max="7" width="28.25" style="2" customWidth="1"/>
-    <col min="8" max="9" width="23.625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.5" customWidth="1"/>
-    <col min="11" max="11" width="12.75" customWidth="1"/>
+    <col min="4" max="5" width="16.125" style="1" customWidth="1"/>
+    <col min="6" max="8" width="21" style="1" customWidth="1"/>
+    <col min="9" max="9" width="28.25" style="1" customWidth="1"/>
+    <col min="10" max="11" width="23.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5" customWidth="1"/>
+    <col min="13" max="13" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1271,208 +1270,282 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>16</v>
+      </c>
+      <c r="L2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E3"/>
       <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G3"/>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="27" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="L3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" ht="27" spans="1:13">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" t="s">
         <v>26</v>
       </c>
-      <c r="K4" t="s">
+      <c r="H4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="B5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" t="b">
+        <v>34</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:13">
       <c r="B6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" t="b">
+        <v>37</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
-      <c r="H6" t="b">
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" t="b">
         <v>1</v>
       </c>
-      <c r="I6"/>
       <c r="J6" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="K6"/>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="B7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7"/>
-      <c r="G7" t="b">
+        <v>37</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" t="b">
         <v>1</v>
       </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7"/>
       <c r="J7" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9"/>
-      <c r="G9" t="b">
+      <c r="K7"/>
+      <c r="L7" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="8" spans="1:13">
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8"/>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8"/>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8"/>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="B10" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" t="b">
+        <v>44</v>
+      </c>
+      <c r="E10"/>
+      <c r="F10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10"/>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11"/>
+      <c r="F11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1486,105 +1559,147 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
-  <cols>
-    <col min="2" max="2" width="12.25" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="11.875" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" t="s">
+        <v>62</v>
+      </c>
+      <c r="I4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="B5" t="b">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" ht="54" spans="1:5">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="B5">
-        <v>1</v>
-      </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="B7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="B8" s="2"/>
+        <v>-40</v>
+      </c>
+      <c r="E5">
+        <v>-40</v>
+      </c>
+      <c r="F5">
+        <v>40</v>
+      </c>
+      <c r="G5">
+        <v>40</v>
+      </c>
+      <c r="H5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" t="s">
+        <v>61</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1593,157 +1708,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" t="s">
-        <v>63</v>
-      </c>
-      <c r="I4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="B5" t="b">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5">
-        <v>-40</v>
-      </c>
-      <c r="E5">
-        <v>-40</v>
-      </c>
-      <c r="F5">
-        <v>40</v>
-      </c>
-      <c r="G5">
-        <v>40</v>
-      </c>
-      <c r="H5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L7"/>
@@ -1761,7 +1725,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="D1" t="s">
         <v>65</v>
@@ -1793,80 +1757,80 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
         <v>74</v>
@@ -1890,16 +1854,16 @@
         <v>80</v>
       </c>
       <c r="I4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J4" t="s">
         <v>61</v>
       </c>
-      <c r="J4" t="s">
-        <v>62</v>
-      </c>
       <c r="K4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1907,13 +1871,13 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
         <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1942,13 +1906,13 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
         <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1957,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I6">
         <v>-50</v>
@@ -1977,13 +1941,13 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
         <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1992,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I7">
         <v>-50</v>

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="area_info" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="84">
   <si>
     <t>##var</t>
   </si>
@@ -225,9 +225,6 @@
     <t>WorldMap/fake_map_fallback</t>
   </si>
   <si>
-    <t>map_id</t>
-  </si>
-  <si>
     <t>region_key</t>
   </si>
   <si>
@@ -258,7 +255,7 @@
     <t>主键</t>
   </si>
   <si>
-    <t>MapName</t>
+    <t>SceneName</t>
   </si>
   <si>
     <t>策划分区名</t>
@@ -280,9 +277,6 @@
   </si>
   <si>
     <t>WorldMap/fake_map_base_01</t>
-  </si>
-  <si>
-    <t>village_01</t>
   </si>
   <si>
     <t>WorldMap/fake_map_village_01</t>
@@ -1561,6 +1555,9 @@
   <sheetPr/>
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <cols>
+    <col min="3" max="3" width="22.75" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
@@ -1725,34 +1722,34 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
         <v>64</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>65</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>66</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>67</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>68</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>69</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>70</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>71</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>72</v>
-      </c>
-      <c r="L1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1833,25 +1830,25 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
         <v>74</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>75</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>76</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>77</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>78</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>79</v>
-      </c>
-      <c r="H4" t="s">
-        <v>80</v>
       </c>
       <c r="I4" t="s">
         <v>60</v>
@@ -1871,10 +1868,10 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
         <v>61</v>
@@ -1886,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I5">
         <v>-50</v>
@@ -1906,10 +1903,10 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
         <v>61</v>
@@ -1921,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I6">
         <v>-50</v>
@@ -1941,10 +1938,10 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
         <v>61</v>
@@ -1956,7 +1953,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I7">
         <v>-50</v>

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="90">
   <si>
     <t>##var</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>map_data_name</t>
+  </si>
+  <si>
+    <t>thumb_map</t>
   </si>
   <si>
     <t>is_home</t>
@@ -1232,20 +1235,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="19.25" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.5" style="1" customWidth="1"/>
     <col min="4" max="5" width="16.125" style="1" customWidth="1"/>
-    <col min="6" max="8" width="21" style="1" customWidth="1"/>
-    <col min="9" max="9" width="28.25" style="1" customWidth="1"/>
-    <col min="10" max="11" width="23.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.75" style="1" customWidth="1"/>
+    <col min="6" max="9" width="21" style="1" customWidth="1"/>
+    <col min="10" max="10" width="28.25" style="1" customWidth="1"/>
+    <col min="11" max="12" width="23.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="12.75" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1288,113 +1291,122 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3"/>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J3" t="s">
         <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" ht="27" customHeight="1" spans="1:14">
+      <c r="O3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" ht="27" customHeight="1" spans="1:15">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
         <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
       </c>
       <c r="I4" t="s">
         <v>29</v>
@@ -1402,144 +1414,159 @@
       <c r="J4" t="s">
         <v>30</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" t="s">
         <v>31</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="N4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="B5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" t="b">
+        <v>36</v>
+      </c>
+      <c r="H5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" t="b">
         <v>1</v>
       </c>
-      <c r="I5" t="b">
+      <c r="J5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15">
       <c r="B6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" t="b">
+        <v>39</v>
+      </c>
+      <c r="H6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" t="b">
         <v>0</v>
-      </c>
-      <c r="J6" t="b">
-        <v>1</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
       </c>
-      <c r="L6"/>
-      <c r="M6" t="b">
+      <c r="L6" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="M6"/>
+      <c r="N6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="B7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" t="s">
         <v>41</v>
       </c>
-      <c r="I7" t="b">
+      <c r="J7" t="b">
         <v>0</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
-      <c r="L7"/>
-      <c r="M7" t="b">
+      <c r="L7" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="M7"/>
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="B8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8"/>
-      <c r="I8" t="b">
+        <v>43</v>
+      </c>
+      <c r="H8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8"/>
+      <c r="J8" t="b">
         <v>0</v>
-      </c>
-      <c r="J8" t="b">
-        <v>1</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
       </c>
-      <c r="L8"/>
-      <c r="M8" t="b">
+      <c r="L8" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="M8"/>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9"/>
@@ -1552,34 +1579,35 @@
       <c r="K9"/>
       <c r="L9"/>
       <c r="M9"/>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="N9"/>
+    </row>
+    <row r="10" spans="1:15">
       <c r="B10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" t="b">
+        <v>46</v>
+      </c>
+      <c r="H10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" t="b">
         <v>0</v>
       </c>
-      <c r="I10" t="b">
+      <c r="J10" t="b">
         <v>1</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
@@ -1590,8 +1618,11 @@
       <c r="M10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="B11"/>
       <c r="C11"/>
       <c r="D11"/>
@@ -1604,53 +1635,60 @@
       <c r="K11"/>
       <c r="L11"/>
       <c r="M11"/>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="N11"/>
+    </row>
+    <row r="12" spans="1:15">
       <c r="B12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12"/>
-      <c r="I12" t="b">
+        <v>49</v>
+      </c>
+      <c r="H12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12"/>
+      <c r="J12" t="b">
         <v>0</v>
       </c>
-      <c r="J12" t="b">
+      <c r="K12" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:15">
       <c r="B13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E13"/>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G13" t="s">
-        <v>51</v>
-      </c>
-      <c r="I13" t="b">
+        <v>52</v>
+      </c>
+      <c r="H13" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" t="b">
         <v>0</v>
       </c>
-      <c r="J13" t="b">
+      <c r="K13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1675,112 +1713,112 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1788,7 +1826,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D5">
         <v>-40</v>
@@ -1803,10 +1841,10 @@
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1836,142 +1874,142 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
       <c r="I2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1979,13 +2017,13 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1994,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I5">
         <v>-50</v>
@@ -2014,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -2029,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I6">
         <v>-50</v>
@@ -2049,13 +2087,13 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -2064,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I7">
         <v>-50</v>

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
   <si>
     <t>##var</t>
   </si>
@@ -55,6 +55,9 @@
     <t>thumb_map</t>
   </si>
   <si>
+    <t>can_teleport</t>
+  </si>
+  <si>
     <t>is_home</t>
   </si>
   <si>
@@ -116,6 +119,9 @@
   </si>
   <si>
     <t>数据文件名</t>
+  </si>
+  <si>
+    <t>传送标记</t>
   </si>
   <si>
     <t>home标记</t>
@@ -1235,20 +1241,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="19.25" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.5" style="1" customWidth="1"/>
     <col min="4" max="5" width="16.125" style="1" customWidth="1"/>
-    <col min="6" max="9" width="21" style="1" customWidth="1"/>
-    <col min="10" max="10" width="28.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="23.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="12.75" style="1" customWidth="1"/>
+    <col min="6" max="10" width="21" style="1" customWidth="1"/>
+    <col min="11" max="11" width="28.25" style="1" customWidth="1"/>
+    <col min="12" max="13" width="23.625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5" style="1" customWidth="1"/>
+    <col min="15" max="15" width="12.75" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1294,279 +1300,315 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="P2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3"/>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K3" t="s">
         <v>22</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" ht="27" customHeight="1" spans="1:15">
+      <c r="P3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" ht="27" customHeight="1" spans="1:16">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
         <v>28</v>
       </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
       <c r="I4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
       <c r="M4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N4" t="s">
         <v>34</v>
       </c>
+      <c r="N4" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="O4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>36</v>
+      </c>
+      <c r="P4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="B5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" t="s">
         <v>38</v>
       </c>
-      <c r="G5" t="s">
-        <v>36</v>
-      </c>
       <c r="H5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>1</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="B6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" t="s">
         <v>41</v>
       </c>
-      <c r="G6" t="s">
-        <v>39</v>
-      </c>
       <c r="H6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
       </c>
       <c r="K6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="b">
         <v>1</v>
       </c>
-      <c r="M6"/>
+      <c r="M6" t="b">
+        <v>1</v>
+      </c>
       <c r="N6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>0</v>
+      </c>
+      <c r="O6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
         <v>42</v>
       </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
       </c>
       <c r="K7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
       </c>
-      <c r="M7"/>
+      <c r="M7" t="b">
+        <v>1</v>
+      </c>
       <c r="N7" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="O7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="B8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E8"/>
       <c r="F8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" t="s">
         <v>45</v>
       </c>
-      <c r="G8" t="s">
-        <v>43</v>
-      </c>
       <c r="H8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8"/>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8"/>
       <c r="K8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
       </c>
-      <c r="M8"/>
+      <c r="M8" t="b">
+        <v>1</v>
+      </c>
       <c r="N8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>0</v>
+      </c>
+      <c r="O8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9"/>
@@ -1580,37 +1622,36 @@
       <c r="L9"/>
       <c r="M9"/>
       <c r="N9"/>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="O9"/>
+    </row>
+    <row r="10" spans="1:16">
       <c r="B10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" t="s">
         <v>48</v>
       </c>
-      <c r="G10" t="s">
-        <v>46</v>
-      </c>
       <c r="H10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="I10"/>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
@@ -1621,8 +1662,11 @@
       <c r="N10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="B11"/>
       <c r="C11"/>
       <c r="D11"/>
@@ -1636,60 +1680,69 @@
       <c r="L11"/>
       <c r="M11"/>
       <c r="N11"/>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="O11"/>
+    </row>
+    <row r="12" spans="1:16">
       <c r="B12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E12"/>
       <c r="F12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" t="s">
         <v>51</v>
       </c>
-      <c r="G12" t="s">
-        <v>49</v>
-      </c>
       <c r="H12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I12"/>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
+      <c r="J12"/>
       <c r="K12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>0</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="B13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E13"/>
       <c r="F13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" t="s">
         <v>54</v>
       </c>
-      <c r="G13" t="s">
-        <v>52</v>
-      </c>
       <c r="H13" t="s">
-        <v>38</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="I13"/>
       <c r="K13" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+      <c r="N13" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,112 +1766,112 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1826,7 +1879,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D5">
         <v>-40</v>
@@ -1841,10 +1894,10 @@
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1874,142 +1927,142 @@
         <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
       <c r="I2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -2017,13 +2070,13 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -2032,7 +2085,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I5">
         <v>-50</v>
@@ -2052,13 +2105,13 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -2067,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I6">
         <v>-50</v>
@@ -2087,13 +2140,13 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -2102,7 +2155,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I7">
         <v>-50</v>

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -4,12 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="area_info" sheetId="1" r:id="rId1"/>
-    <sheet name="world_map_global" sheetId="2" r:id="rId2"/>
-    <sheet name="world_map_big_map" sheetId="3" r:id="rId3"/>
+    <sheet name="logic_area_info" sheetId="4" r:id="rId1"/>
+    <sheet name="area_variant_info" sheetId="1" r:id="rId2"/>
+    <sheet name="area_overlay_state_info" sheetId="5" r:id="rId3"/>
+    <sheet name="world_map_global" sheetId="2" r:id="rId4"/>
+    <sheet name="world_map_big_map" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,41 +31,137 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="97">
   <si>
     <t>##var</t>
   </si>
   <si>
+    <t>map_id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c,s</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>base_01</t>
+  </si>
+  <si>
+    <t>据点</t>
+  </si>
+  <si>
+    <t>village_01</t>
+  </si>
+  <si>
+    <t>村子1</t>
+  </si>
+  <si>
+    <t>village_02</t>
+  </si>
+  <si>
+    <t>村子2</t>
+  </si>
+  <si>
+    <t>var_id</t>
   </si>
   <si>
     <t>desc</t>
   </si>
   <si>
+    <t>logic_area_id</t>
+  </si>
+  <si>
+    <t>scene_name</t>
+  </si>
+  <si>
+    <t>thumb_map</t>
+  </si>
+  <si>
+    <t>is_secret_base</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>逻辑区域id</t>
+  </si>
+  <si>
+    <t>场景名</t>
+  </si>
+  <si>
+    <t>隐秘据点</t>
+  </si>
+  <si>
+    <t>secret_base_hub</t>
+  </si>
+  <si>
+    <t>隐秘据点横板场景</t>
+  </si>
+  <si>
+    <t>Main_Home</t>
+  </si>
+  <si>
+    <t>Main_Area_01</t>
+  </si>
+  <si>
+    <t>Main_Area_02</t>
+  </si>
+  <si>
+    <t>game_init</t>
+  </si>
+  <si>
+    <t>出生点</t>
+  </si>
+  <si>
+    <t>Main_Init</t>
+  </si>
+  <si>
+    <t>base_01_fight</t>
+  </si>
+  <si>
+    <t>纷争据点</t>
+  </si>
+  <si>
+    <t>Main_Home_Fight</t>
+  </si>
+  <si>
     <t>day_period_limit</t>
   </si>
   <si>
-    <t>scene_name</t>
-  </si>
-  <si>
     <t>map_data_name</t>
   </si>
   <si>
-    <t>thumb_map</t>
-  </si>
-  <si>
     <t>can_teleport</t>
   </si>
   <si>
     <t>is_home</t>
   </si>
   <si>
-    <t>is_secret_base</t>
-  </si>
-  <si>
     <t>always_alert</t>
   </si>
   <si>
@@ -79,45 +177,15 @@
     <t>hunting_unlock_conds</t>
   </si>
   <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
-    <t>bool</t>
-  </si>
-  <si>
     <t>(list#sep=;),CommonCheckCond</t>
   </si>
   <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c,s</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
     <t>时间要求</t>
   </si>
   <si>
-    <t>场景名</t>
-  </si>
-  <si>
     <t>数据文件名</t>
   </si>
   <si>
@@ -125,9 +193,6 @@
   </si>
   <si>
     <t>home标记</t>
-  </si>
-  <si>
-    <t>隐秘据点</t>
   </si>
   <si>
     <t>警戒标记</t>
@@ -147,63 +212,15 @@
     <t>解锁条件</t>
   </si>
   <si>
-    <t>base_01</t>
-  </si>
-  <si>
-    <t>据点</t>
-  </si>
-  <si>
-    <t>Main_Home</t>
-  </si>
-  <si>
     <t>village_01_d</t>
   </si>
   <si>
-    <t>村子1</t>
-  </si>
-  <si>
-    <t>Main_Area_01</t>
-  </si>
-  <si>
     <t>village_01_n</t>
   </si>
   <si>
-    <t>village_02</t>
-  </si>
-  <si>
-    <t>村子2</t>
-  </si>
-  <si>
-    <t>Main_Area_02</t>
-  </si>
-  <si>
-    <t>secret_base_hub</t>
-  </si>
-  <si>
-    <t>隐秘据点横板场景</t>
-  </si>
-  <si>
-    <t>Main_SecretBase</t>
-  </si>
-  <si>
-    <t>game_init</t>
-  </si>
-  <si>
-    <t>出生点</t>
-  </si>
-  <si>
-    <t>Main_Init</t>
-  </si>
-  <si>
     <t>base_fight</t>
   </si>
   <si>
-    <t>纷争据点</t>
-  </si>
-  <si>
-    <t>Main_Home_Fight</t>
-  </si>
-  <si>
     <t>allow_open_when_area_unknown</t>
   </si>
   <si>
@@ -249,6 +266,12 @@
     <t>WorldMap/fake_map_fallback</t>
   </si>
   <si>
+    <t>area_var_id</t>
+  </si>
+  <si>
+    <t>is_main</t>
+  </si>
+  <si>
     <t>region_key</t>
   </si>
   <si>
@@ -261,7 +284,7 @@
     <t>forbid_open_world_map</t>
   </si>
   <si>
-    <t>big_map_texture_resource_path</t>
+    <t>big_map_texture_path</t>
   </si>
   <si>
     <t>world_min_x</t>
@@ -279,7 +302,10 @@
     <t>主键</t>
   </si>
   <si>
-    <t>SceneName</t>
+    <t>所属map变体</t>
+  </si>
+  <si>
+    <t>是否为主要</t>
   </si>
   <si>
     <t>策划分区名</t>
@@ -298,15 +324,6 @@
   </si>
   <si>
     <t>default</t>
-  </si>
-  <si>
-    <t>WorldMap/fake_map_base_01</t>
-  </si>
-  <si>
-    <t>WorldMap/fake_map_village_01</t>
-  </si>
-  <si>
-    <t>WorldMap/fake_map_game_init</t>
   </si>
 </sst>
 </file>
@@ -1241,507 +1258,345 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="2"/>
+  <cols>
+    <col min="2" max="2" width="16.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="19.25" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.5" style="1" customWidth="1"/>
     <col min="4" max="5" width="16.125" style="1" customWidth="1"/>
-    <col min="6" max="10" width="21" style="1" customWidth="1"/>
-    <col min="11" max="11" width="28.25" style="1" customWidth="1"/>
-    <col min="12" max="13" width="23.625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5" style="1" customWidth="1"/>
-    <col min="15" max="15" width="12.75" style="1" customWidth="1"/>
+    <col min="6" max="7" width="21" style="1" customWidth="1"/>
+    <col min="8" max="8" width="28.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" t="s">
-        <v>19</v>
-      </c>
-      <c r="P2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" t="s">
-        <v>21</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3"/>
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>6</v>
+      </c>
       <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3" t="s">
-        <v>22</v>
-      </c>
-      <c r="O3" t="s">
-        <v>22</v>
-      </c>
-      <c r="P3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" ht="27" customHeight="1" spans="1:16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" ht="27" customHeight="1" spans="1:8">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>26</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
         <v>27</v>
       </c>
-      <c r="F4" t="s">
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:8">
+      <c r="B5" t="s">
         <v>28</v>
       </c>
-      <c r="G4" t="s">
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
         <v>29</v>
       </c>
-      <c r="H4" t="s">
+      <c r="E5" t="s">
         <v>28</v>
       </c>
-      <c r="I4" t="s">
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:8">
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
         <v>30</v>
       </c>
-      <c r="J4" t="s">
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
         <v>31</v>
       </c>
-      <c r="K4" t="s">
+      <c r="G8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
         <v>32</v>
       </c>
-      <c r="L4" t="s">
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="B11" t="s">
         <v>33</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="C11" t="s">
         <v>34</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" t="s">
         <v>35</v>
       </c>
-      <c r="O4" t="s">
+      <c r="G11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="B12" t="s">
         <v>36</v>
       </c>
-      <c r="P4" t="s">
+      <c r="C12" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="B5" t="s">
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
         <v>38</v>
       </c>
-      <c r="C5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" t="b">
-        <v>1</v>
-      </c>
-      <c r="N6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="B7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" t="s">
-        <v>43</v>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" t="b">
-        <v>1</v>
-      </c>
-      <c r="N7" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="B8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8"/>
-      <c r="F8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8"/>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" t="b">
-        <v>1</v>
-      </c>
-      <c r="N8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="B9"/>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
-      <c r="L9"/>
-      <c r="M9"/>
-      <c r="N9"/>
-      <c r="O9"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I10"/>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" t="b">
-        <v>1</v>
-      </c>
-      <c r="L10" t="b">
-        <v>0</v>
-      </c>
-      <c r="M10" t="b">
-        <v>0</v>
-      </c>
-      <c r="N10" t="b">
-        <v>0</v>
-      </c>
-      <c r="O10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11"/>
-      <c r="K11"/>
-      <c r="L11"/>
-      <c r="M11"/>
-      <c r="N11"/>
-      <c r="O11"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="B12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12"/>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
       <c r="G12" t="s">
-        <v>51</v>
-      </c>
-      <c r="H12" t="s">
-        <v>53</v>
-      </c>
-      <c r="I12"/>
-      <c r="J12"/>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="b">
-        <v>1</v>
-      </c>
-      <c r="N12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="B13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13"/>
-      <c r="F13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" t="s">
-        <v>54</v>
-      </c>
-      <c r="H13" t="s">
-        <v>40</v>
-      </c>
-      <c r="I13"/>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" t="b">
-        <v>1</v>
-      </c>
-      <c r="N13" t="b">
+        <v>10</v>
+      </c>
+      <c r="H12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1752,7 +1607,479 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:O16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="2" max="2" width="12.125" customWidth="1"/>
+    <col min="3" max="3" width="12.625" customWidth="1"/>
+    <col min="4" max="4" width="11.625" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="7" max="7" width="15.875" customWidth="1"/>
+    <col min="8" max="8" width="13.625" customWidth="1"/>
+    <col min="11" max="11" width="12.625" customWidth="1"/>
+    <col min="12" max="12" width="15.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N3" t="s">
+        <v>6</v>
+      </c>
+      <c r="O3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" ht="67.5" spans="1:15">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N4" t="s">
+        <v>57</v>
+      </c>
+      <c r="O4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1"/>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="B8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1"/>
+      <c r="M12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" t="s">
+        <v>61</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1"/>
+      <c r="M13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="N14" s="1"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="N15" s="1"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I5"/>
@@ -1766,65 +2093,65 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="I1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
@@ -1847,31 +2174,31 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1879,7 +2206,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D5">
         <v>-40</v>
@@ -1894,10 +2221,10 @@
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1906,102 +2233,108 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
-    <col min="3" max="3" width="17.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="33.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.625" customWidth="1"/>
+    <col min="9" max="9" width="33.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K1" t="s">
+        <v>85</v>
+      </c>
+      <c r="L1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2" t="s">
+        <v>70</v>
+      </c>
+      <c r="L2" t="s">
+        <v>70</v>
+      </c>
+      <c r="M2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J1" t="s">
-        <v>78</v>
-      </c>
-      <c r="K1" t="s">
-        <v>79</v>
-      </c>
-      <c r="L1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J2" t="s">
-        <v>65</v>
-      </c>
-      <c r="K2" t="s">
-        <v>65</v>
-      </c>
-      <c r="L2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
       <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D3"/>
       <c r="E3" t="s">
         <v>23</v>
       </c>
@@ -2026,147 +2359,162 @@
       <c r="L3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F4" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G4" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="H4" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="I4" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="J4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="L4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>74</v>
+      </c>
+      <c r="M4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" t="s">
-        <v>88</v>
+        <v>10</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>89</v>
-      </c>
-      <c r="I5">
-        <v>-50</v>
+        <v>96</v>
+      </c>
+      <c r="F5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="s">
+        <v>10</v>
       </c>
       <c r="J5">
         <v>-50</v>
       </c>
       <c r="K5">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="L5">
         <v>50</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" t="s">
-        <v>88</v>
+        <v>12</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>90</v>
-      </c>
-      <c r="I6">
-        <v>-50</v>
+        <v>96</v>
+      </c>
+      <c r="F6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="s">
+        <v>12</v>
       </c>
       <c r="J6">
         <v>-50</v>
       </c>
       <c r="K6">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="L6">
         <v>50</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="M6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" t="s">
-        <v>88</v>
+        <v>14</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>91</v>
-      </c>
-      <c r="I7">
-        <v>-50</v>
+        <v>96</v>
+      </c>
+      <c r="F7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="s">
+        <v>14</v>
       </c>
       <c r="J7">
         <v>-50</v>
       </c>
       <c r="K7">
+        <v>-50</v>
+      </c>
+      <c r="L7">
         <v>50</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>50</v>
       </c>
     </row>

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="2"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="logic_area_info" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="102">
   <si>
     <t>##var</t>
   </si>
@@ -90,6 +90,12 @@
     <t>logic_area_id</t>
   </si>
   <si>
+    <t>show_in_map</t>
+  </si>
+  <si>
+    <t>show_conds</t>
+  </si>
+  <si>
     <t>scene_name</t>
   </si>
   <si>
@@ -102,6 +108,9 @@
     <t>bool</t>
   </si>
   <si>
+    <t>(list#sep=;),CommonCheckCond</t>
+  </si>
+  <si>
     <t>c</t>
   </si>
   <si>
@@ -111,6 +120,12 @@
     <t>逻辑区域id</t>
   </si>
   <si>
+    <t>是否显示</t>
+  </si>
+  <si>
+    <t>显示条件</t>
+  </si>
+  <si>
     <t>场景名</t>
   </si>
   <si>
@@ -181,9 +196,6 @@
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>(list#sep=;),CommonCheckCond</t>
   </si>
   <si>
     <t>时间要求</t>
@@ -1341,17 +1353,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="19.25" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.5" style="1" customWidth="1"/>
-    <col min="4" max="5" width="16.125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="21" style="1" customWidth="1"/>
-    <col min="8" max="8" width="28.25" style="1" customWidth="1"/>
+    <col min="4" max="7" width="16.125" style="1" customWidth="1"/>
+    <col min="8" max="9" width="21" style="1" customWidth="1"/>
+    <col min="10" max="10" width="28.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1376,8 +1388,14 @@
       <c r="H1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1394,16 +1412,22 @@
         <v>4</v>
       </c>
       <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>4</v>
       </c>
-      <c r="H2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1412,20 +1436,26 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E3"/>
       <c r="F3" t="s">
         <v>6</v>
       </c>
       <c r="G3" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" ht="27" customHeight="1" spans="1:8">
+      <c r="I3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" ht="27" customHeight="1" spans="1:10">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1436,43 +1466,51 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:8">
+        <v>31</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:10">
       <c r="B5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>30</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F5"/>
       <c r="G5"/>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="1:8">
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5"/>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" spans="1:10">
       <c r="B6"/>
       <c r="C6"/>
       <c r="D6"/>
@@ -1480,8 +1518,10 @@
       <c r="F6"/>
       <c r="G6"/>
       <c r="H6"/>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6"/>
+      <c r="J6"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="B7" t="s">
         <v>10</v>
       </c>
@@ -1494,17 +1534,21 @@
       <c r="E7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7"/>
+      <c r="H7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" t="s">
         <v>10</v>
       </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="B8" t="s">
         <v>12</v>
       </c>
@@ -1517,17 +1561,21 @@
       <c r="E8" t="s">
         <v>12</v>
       </c>
-      <c r="F8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8"/>
+      <c r="H8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" t="s">
         <v>12</v>
       </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" t="s">
         <v>14</v>
       </c>
@@ -1540,17 +1588,21 @@
       <c r="E9" t="s">
         <v>14</v>
       </c>
-      <c r="F9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9"/>
+      <c r="H9" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" t="s">
         <v>14</v>
       </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="B10"/>
       <c r="C10"/>
       <c r="D10"/>
@@ -1558,50 +1610,56 @@
       <c r="F10"/>
       <c r="G10"/>
       <c r="H10"/>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10"/>
+      <c r="J10"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="B11" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>39</v>
+      </c>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="B12" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
-      <c r="F12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" t="s">
         <v>10</v>
       </c>
-      <c r="H12" t="b">
+      <c r="J12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1626,6 +1684,8 @@
     <col min="8" max="8" width="13.625" style="1" customWidth="1"/>
     <col min="11" max="11" width="12.625" style="1" customWidth="1"/>
     <col min="12" max="12" width="15.125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.625" customWidth="1"/>
+    <col min="14" max="14" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -1645,34 +1705,34 @@
         <v>16</v>
       </c>
       <c r="F1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="J1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="L1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="O1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -1692,34 +1752,34 @@
         <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G2" t="s">
         <v>4</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O2" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -1730,7 +1790,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
         <v>6</v>
@@ -1742,7 +1802,7 @@
         <v>6</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
         <v>6</v>
@@ -1754,7 +1814,7 @@
         <v>6</v>
       </c>
       <c r="O3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" ht="67.5" customHeight="1" spans="1:15">
@@ -1768,60 +1828,60 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="N4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="O4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="B5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -1880,7 +1940,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="B8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
@@ -1895,7 +1955,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -1918,7 +1978,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="B9" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
@@ -1933,7 +1993,7 @@
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -1994,19 +2054,19 @@
     </row>
     <row r="12" spans="1:15">
       <c r="B12" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
@@ -2023,19 +2083,19 @@
     </row>
     <row r="13" spans="1:15">
       <c r="B13" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G13" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
@@ -2070,28 +2130,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2099,22 +2159,22 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H2" t="s">
         <v>4</v>
@@ -2131,22 +2191,22 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2154,28 +2214,28 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2183,7 +2243,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D5">
         <v>-40</v>
@@ -2198,10 +2258,10 @@
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2230,37 +2290,37 @@
         <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="I1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="M1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -2268,13 +2328,13 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>4</v>
@@ -2283,25 +2343,25 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
         <v>4</v>
       </c>
       <c r="J2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="L2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="M2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2313,31 +2373,31 @@
       </c>
       <c r="D3"/>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2345,40 +2405,40 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2392,10 +2452,10 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2430,10 +2490,10 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2468,10 +2528,10 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G7">
         <v>0</v>

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="logic_area_info" sheetId="1" r:id="rId1"/>
@@ -278,7 +278,7 @@
     <t>逗号分隔</t>
   </si>
   <si>
-    <t>WorldMap/fake_map_fallback</t>
+    <t>fallback</t>
   </si>
   <si>
     <t>area_var_id</t>

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="4"/>
+    <workbookView windowHeight="17655" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="logic_area_info" sheetId="1" r:id="rId1"/>

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="logic_area_info" sheetId="1" state="visible" r:id="rId1"/>
@@ -1008,7 +1008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col width="16.375" customWidth="1" style="1" min="2" max="2"/>
@@ -1030,6 +1030,11 @@
           <t>name</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>can_annex_homestead</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -1047,6 +1052,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -1059,6 +1069,11 @@
           <t>c,s</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
@@ -1076,6 +1091,11 @@
           <t>名称</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>可收编为家园</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="0" t="inlineStr">
@@ -1088,6 +1108,9 @@
           <t>家园小镇</t>
         </is>
       </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="0" t="inlineStr">
@@ -1100,6 +1123,9 @@
           <t>村子1</t>
         </is>
       </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="0" t="inlineStr">
@@ -1111,6 +1137,9 @@
         <is>
           <t>村子2</t>
         </is>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2155,7 +2184,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="B12" s="0" t="inlineStr">
         <is>

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="logic_area_info" sheetId="1" r:id="rId1"/>

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="logic_area_info" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="113">
   <si>
     <t>##var</t>
   </si>
@@ -205,6 +205,9 @@
   </si>
   <si>
     <t>procedural_def_id</t>
+  </si>
+  <si>
+    <t>peace_zone_mark</t>
   </si>
   <si>
     <t>int</t>
@@ -240,6 +243,9 @@
   </si>
   <si>
     <t>程序生成定义 id</t>
+  </si>
+  <si>
+    <t>全图安全区标记</t>
   </si>
   <si>
     <t>village_01_d</t>
@@ -1721,7 +1727,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="12.125" style="1" customWidth="1"/>
@@ -1736,7 +1742,7 @@
     <col min="14" max="14" width="14.75" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1785,8 +1791,11 @@
       <c r="P1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1803,7 +1812,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G2" t="s">
         <v>5</v>
@@ -1835,8 +1844,11 @@
       <c r="P2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1873,8 +1885,11 @@
       <c r="P3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" ht="67.5" customHeight="1" spans="1:16">
+      <c r="Q3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="67.5" customHeight="1" spans="1:17">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1891,40 +1906,43 @@
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J4" t="s">
         <v>34</v>
       </c>
       <c r="K4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <v>69</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="B5" t="s">
         <v>35</v>
       </c>
@@ -1958,12 +1976,15 @@
       <c r="N5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:17">
       <c r="B7" t="s">
         <v>13</v>
       </c>
@@ -1997,8 +2018,11 @@
       <c r="M7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="B8"/>
       <c r="C8"/>
       <c r="D8"/>
@@ -2008,9 +2032,9 @@
       <c r="L8"/>
       <c r="M8"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:17">
       <c r="B9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
         <v>16</v>
@@ -2025,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -2045,10 +2069,13 @@
       <c r="N9" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="B10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
         <v>16</v>
@@ -2063,7 +2090,7 @@
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -2083,8 +2110,11 @@
       <c r="N10" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="B11" t="s">
         <v>17</v>
       </c>
@@ -2121,8 +2151,11 @@
       <c r="N11" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="B13" t="s">
         <v>41</v>
       </c>
@@ -2150,8 +2183,11 @@
       <c r="M13" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="B14" t="s">
         <v>44</v>
       </c>
@@ -2165,7 +2201,7 @@
         <v>44</v>
       </c>
       <c r="G14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
@@ -2179,20 +2215,23 @@
       <c r="M14" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="B15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" t="s">
         <v>74</v>
       </c>
-      <c r="E15" t="s">
-        <v>72</v>
-      </c>
       <c r="F15">
         <v>0</v>
       </c>
@@ -2218,7 +2257,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>75</v>
+        <v>77</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2241,28 +2283,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2276,16 +2318,16 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H2" t="s">
         <v>5</v>
@@ -2325,28 +2367,28 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2354,7 +2396,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D5">
         <v>-40</v>
@@ -2369,10 +2411,10 @@
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2401,37 +2443,37 @@
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -2439,7 +2481,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
@@ -2454,7 +2496,7 @@
         <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H2" t="s">
         <v>6</v>
@@ -2463,16 +2505,16 @@
         <v>5</v>
       </c>
       <c r="J2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2516,40 +2558,40 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2563,10 +2605,10 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2601,10 +2643,10 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2639,10 +2681,10 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G7">
         <v>0</v>

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -1632,12 +1632,12 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>测试连通A</t>
+          <t>初始地下城外地图</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>测试连通A</t>
+          <t>初始地下城外地图</t>
         </is>
       </c>
       <c r="E13" s="0" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>base_fight</t>
+          <t>home_01_fight</t>
         </is>
       </c>
       <c r="H14" s="0" t="b">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>测试连通A</t>
+          <t>初始地下城外地图</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>测试连通A</t>
+          <t>初始地下城外地图</t>
         </is>
       </c>
       <c r="E16" s="0" t="inlineStr">

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -1008,7 +1008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col width="16.375" customWidth="1" style="1" min="2" max="2"/>
@@ -1154,6 +1154,36 @@
         </is>
       </c>
       <c r="D8" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>test_link_a</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Initial Dungeon Outskirts</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>test_link_b</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Home East Outskirts</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1665,12 +1695,12 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>测试连通B</t>
+          <t>Home East Outskirts</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>测试连通B</t>
+          <t>Transition area east of home_01 leading to forest_01</t>
         </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
@@ -2549,12 +2579,12 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>测试连通B</t>
+          <t>Home East Outskirts</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>测试连通B</t>
+          <t>Transition area east of home_01 leading to forest_01</t>
         </is>
       </c>
       <c r="E17" s="0" t="inlineStr">
@@ -2571,7 +2601,7 @@
         </is>
       </c>
       <c r="H17" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" s="0" t="b">
         <v>0</v>

--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -1,19 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="logic_area_info" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="area_variant_info" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="area_overlay_state_info" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="world_map_global" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="world_map_big_map" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="logic_area_info" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="area_variant_info" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="area_overlay_state_info" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="world_map_global" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="world_map_big_map" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -23,154 +19,112 @@
   <fonts count="20">
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF0000FF"/>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF800080"/>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FFFF0000"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="18"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <i val="1"/>
       <color rgb="FF7F7F7F"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="15"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="13"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF3F3F76"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <b val="1"/>
       <color rgb="FF3F3F3F"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <b val="1"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF006100"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color theme="0"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -183,198 +137,161 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="4" tint="0.79998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="4" tint="0.59999"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="4" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="5" tint="0.79998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="5" tint="0.59999"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="5" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="6" tint="0.79998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="6" tint="0.59999"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="6" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7" tint="0.79998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7" tint="0.59999"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="8" tint="0.79998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="8" tint="0.59999"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="8" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="9" tint="0.79998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="9" tint="0.59999"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="9" tint="0.39998"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="9">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
@@ -388,25 +305,16 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -421,7 +329,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -436,7 +343,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -451,46 +357,38 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="19" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
@@ -499,7 +397,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
@@ -633,57 +531,56 @@
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0"/>
+    <cellStyle name="千位分隔" xfId="1"/>
+    <cellStyle name="货币" xfId="2"/>
+    <cellStyle name="百分比" xfId="3"/>
+    <cellStyle name="千位分隔[0]" xfId="4"/>
+    <cellStyle name="货币[0]" xfId="5"/>
+    <cellStyle name="超链接" xfId="6"/>
+    <cellStyle name="已访问的超链接" xfId="7"/>
+    <cellStyle name="注释" xfId="8"/>
+    <cellStyle name="警告文本" xfId="9"/>
+    <cellStyle name="标题" xfId="10"/>
+    <cellStyle name="解释性文本" xfId="11"/>
+    <cellStyle name="标题 1" xfId="12"/>
+    <cellStyle name="标题 2" xfId="13"/>
+    <cellStyle name="标题 3" xfId="14"/>
+    <cellStyle name="标题 4" xfId="15"/>
+    <cellStyle name="输入" xfId="16"/>
+    <cellStyle name="输出" xfId="17"/>
+    <cellStyle name="计算" xfId="18"/>
+    <cellStyle name="检查单元格" xfId="19"/>
+    <cellStyle name="链接单元格" xfId="20"/>
+    <cellStyle name="汇总" xfId="21"/>
+    <cellStyle name="好" xfId="22"/>
+    <cellStyle name="差" xfId="23"/>
+    <cellStyle name="适中" xfId="24"/>
+    <cellStyle name="强调文字颜色 1" xfId="25"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
+    <cellStyle name="强调文字颜色 2" xfId="29"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
+    <cellStyle name="强调文字颜色 3" xfId="33"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
+    <cellStyle name="强调文字颜色 4" xfId="37"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
+    <cellStyle name="强调文字颜色 5" xfId="41"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
+    <cellStyle name="强调文字颜色 6" xfId="45"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -796,76 +693,16 @@
         <a:srgbClr val="7E1FAD"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="WPS">
@@ -889,9 +726,7 @@
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr"/>
@@ -901,27 +736,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:gradFill>
             <a:gsLst>
               <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
+                <a:schemeClr val="phClr"/>
               </a:gs>
               <a:gs pos="100000">
                 <a:schemeClr val="phClr"/>
@@ -930,7 +761,6 @@
             <a:lin ang="2700000" scaled="1"/>
           </a:gradFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -973,17 +803,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -998,7 +828,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
@@ -1008,8 +837,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.375" customWidth="1" style="1" min="2" max="2"/>
   </cols>
@@ -1187,8 +1016,23 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>village_01_road</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>晨钟镇南北道</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1198,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="19.25" customWidth="1" style="1" min="2" max="2"/>
@@ -1758,9 +1602,46 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>village_01_road</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>晨钟镇南北道</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>家园与晨钟镇之间的南北过渡道路</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>village_01_road</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>Village01_Road</t>
+        </is>
+      </c>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>village_01_road</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -1770,7 +1651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12.125" customWidth="1" style="1" min="2" max="2"/>
@@ -1871,6 +1752,56 @@
           <t>peace_zone_mark</t>
         </is>
       </c>
+      <c r="R1" s="0" t="inlineStr">
+        <is>
+          <t>walker_limit</t>
+        </is>
+      </c>
+      <c r="S1" s="0" t="inlineStr">
+        <is>
+          <t>walker_spawn_interval</t>
+        </is>
+      </c>
+      <c r="T1" s="0" t="inlineStr">
+        <is>
+          <t>walker_hot_radius</t>
+        </is>
+      </c>
+      <c r="U1" s="0" t="inlineStr">
+        <is>
+          <t>walker_hidden_radius</t>
+        </is>
+      </c>
+      <c r="V1" s="0" t="inlineStr">
+        <is>
+          <t>walker_normal_weight</t>
+        </is>
+      </c>
+      <c r="W1" s="0" t="inlineStr">
+        <is>
+          <t>walker_advanced_weight</t>
+        </is>
+      </c>
+      <c r="X1" s="0" t="inlineStr">
+        <is>
+          <t>walker_elite_weight</t>
+        </is>
+      </c>
+      <c r="Y1" s="0" t="inlineStr">
+        <is>
+          <t>walker_normal_cfg_id</t>
+        </is>
+      </c>
+      <c r="Z1" s="0" t="inlineStr">
+        <is>
+          <t>walker_advanced_cfg_id</t>
+        </is>
+      </c>
+      <c r="AA1" s="0" t="inlineStr">
+        <is>
+          <t>walker_elite_cfg_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -1958,6 +1889,56 @@
           <t>bool</t>
         </is>
       </c>
+      <c r="R2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="S2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="T2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="U2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="V2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="W2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="X2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="Y2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Z2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AA2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -2025,6 +2006,28 @@
           <t>c,s</t>
         </is>
       </c>
+      <c r="R3" s="0" t="n"/>
+      <c r="S3" s="0" t="n"/>
+      <c r="T3" s="0" t="n"/>
+      <c r="U3" s="0" t="n"/>
+      <c r="V3" s="0" t="n"/>
+      <c r="W3" s="0" t="n"/>
+      <c r="X3" s="0" t="n"/>
+      <c r="Y3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="Z3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="AA3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="67.5" customHeight="1" s="1">
       <c r="A4" s="0" t="inlineStr">
@@ -2114,6 +2117,56 @@
           <t>全图安全区标记</t>
         </is>
       </c>
+      <c r="R4" s="0" t="inlineStr">
+        <is>
+          <t>路人数量上限</t>
+        </is>
+      </c>
+      <c r="S4" s="0" t="inlineStr">
+        <is>
+          <t>刷新间隔</t>
+        </is>
+      </c>
+      <c r="T4" s="0" t="inlineStr">
+        <is>
+          <t>玩家热区半径</t>
+        </is>
+      </c>
+      <c r="U4" s="0" t="inlineStr">
+        <is>
+          <t>玩家近身不可见半径</t>
+        </is>
+      </c>
+      <c r="V4" s="0" t="inlineStr">
+        <is>
+          <t>普通权重</t>
+        </is>
+      </c>
+      <c r="W4" s="0" t="inlineStr">
+        <is>
+          <t>高级权重</t>
+        </is>
+      </c>
+      <c r="X4" s="0" t="inlineStr">
+        <is>
+          <t>精英权重</t>
+        </is>
+      </c>
+      <c r="Y4" s="0" t="inlineStr">
+        <is>
+          <t>普通市民CfgId</t>
+        </is>
+      </c>
+      <c r="Z4" s="0" t="inlineStr">
+        <is>
+          <t>高级市民CfgId</t>
+        </is>
+      </c>
+      <c r="AA4" s="0" t="inlineStr">
+        <is>
+          <t>精英市民CfgId</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="0" t="inlineStr">
@@ -2162,10 +2215,30 @@
       <c r="Q5" s="0" t="b">
         <v>0</v>
       </c>
+      <c r="R5" s="0" t="n"/>
+      <c r="S5" s="0" t="n"/>
+      <c r="T5" s="0" t="n"/>
+      <c r="U5" s="0" t="n"/>
+      <c r="V5" s="0" t="n"/>
+      <c r="W5" s="0" t="n"/>
+      <c r="X5" s="0" t="n"/>
+      <c r="Y5" s="0" t="n"/>
+      <c r="Z5" s="0" t="n"/>
+      <c r="AA5" s="0" t="n"/>
     </row>
     <row r="6">
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
+      <c r="R6" s="0" t="n"/>
+      <c r="S6" s="0" t="n"/>
+      <c r="T6" s="0" t="n"/>
+      <c r="U6" s="0" t="n"/>
+      <c r="V6" s="0" t="n"/>
+      <c r="W6" s="0" t="n"/>
+      <c r="X6" s="0" t="n"/>
+      <c r="Y6" s="0" t="n"/>
+      <c r="Z6" s="0" t="n"/>
+      <c r="AA6" s="0" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="0" t="inlineStr">
@@ -2213,6 +2286,42 @@
       </c>
       <c r="Q7" s="0" t="b">
         <v>1</v>
+      </c>
+      <c r="R7" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="S7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="U7" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="W7" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="X7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="0" t="inlineStr">
+        <is>
+          <t>civil</t>
+        </is>
+      </c>
+      <c r="Z7" s="0" t="inlineStr">
+        <is>
+          <t>civil_advanced</t>
+        </is>
+      </c>
+      <c r="AA7" s="0" t="inlineStr">
+        <is>
+          <t>civil_elite</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -2224,6 +2333,16 @@
       <c r="H8" s="0" t="n"/>
       <c r="L8" s="0" t="n"/>
       <c r="M8" s="0" t="n"/>
+      <c r="R8" s="0" t="n"/>
+      <c r="S8" s="0" t="n"/>
+      <c r="T8" s="0" t="n"/>
+      <c r="U8" s="0" t="n"/>
+      <c r="V8" s="0" t="n"/>
+      <c r="W8" s="0" t="n"/>
+      <c r="X8" s="0" t="n"/>
+      <c r="Y8" s="0" t="n"/>
+      <c r="Z8" s="0" t="n"/>
+      <c r="AA8" s="0" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="0" t="inlineStr">
@@ -2275,6 +2394,42 @@
       <c r="Q9" s="0" t="b">
         <v>0</v>
       </c>
+      <c r="R9" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="S9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="U9" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="W9" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="X9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="0" t="inlineStr">
+        <is>
+          <t>civil</t>
+        </is>
+      </c>
+      <c r="Z9" s="0" t="inlineStr">
+        <is>
+          <t>civil_advanced</t>
+        </is>
+      </c>
+      <c r="AA9" s="0" t="inlineStr">
+        <is>
+          <t>civil_elite</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="0" t="inlineStr">
@@ -2326,6 +2481,42 @@
       <c r="Q10" s="0" t="b">
         <v>0</v>
       </c>
+      <c r="R10" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="S10" s="0" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T10" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="U10" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="W10" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="X10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="0" t="inlineStr">
+        <is>
+          <t>civil</t>
+        </is>
+      </c>
+      <c r="Z10" s="0" t="inlineStr">
+        <is>
+          <t>civil_advanced</t>
+        </is>
+      </c>
+      <c r="AA10" s="0" t="inlineStr">
+        <is>
+          <t>civil_elite</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="0" t="inlineStr">
@@ -2377,8 +2568,55 @@
       <c r="Q11" s="0" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12"/>
+      <c r="R11" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="S11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="U11" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="W11" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="X11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="0" t="inlineStr">
+        <is>
+          <t>civil</t>
+        </is>
+      </c>
+      <c r="Z11" s="0" t="inlineStr">
+        <is>
+          <t>civil_advanced</t>
+        </is>
+      </c>
+      <c r="AA11" s="0" t="inlineStr">
+        <is>
+          <t>civil_elite</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="R12" s="0" t="n"/>
+      <c r="S12" s="0" t="n"/>
+      <c r="T12" s="0" t="n"/>
+      <c r="U12" s="0" t="n"/>
+      <c r="V12" s="0" t="n"/>
+      <c r="W12" s="0" t="n"/>
+      <c r="X12" s="0" t="n"/>
+      <c r="Y12" s="0" t="n"/>
+      <c r="Z12" s="0" t="n"/>
+      <c r="AA12" s="0" t="n"/>
+    </row>
     <row r="13">
       <c r="B13" s="0" t="inlineStr">
         <is>
@@ -2420,6 +2658,16 @@
       <c r="Q13" s="0" t="b">
         <v>0</v>
       </c>
+      <c r="R13" s="0" t="n"/>
+      <c r="S13" s="0" t="n"/>
+      <c r="T13" s="0" t="n"/>
+      <c r="U13" s="0" t="n"/>
+      <c r="V13" s="0" t="n"/>
+      <c r="W13" s="0" t="n"/>
+      <c r="X13" s="0" t="n"/>
+      <c r="Y13" s="0" t="n"/>
+      <c r="Z13" s="0" t="n"/>
+      <c r="AA13" s="0" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="0" t="inlineStr">
@@ -2462,6 +2710,16 @@
       <c r="Q14" s="0" t="b">
         <v>0</v>
       </c>
+      <c r="R14" s="0" t="n"/>
+      <c r="S14" s="0" t="n"/>
+      <c r="T14" s="0" t="n"/>
+      <c r="U14" s="0" t="n"/>
+      <c r="V14" s="0" t="n"/>
+      <c r="W14" s="0" t="n"/>
+      <c r="X14" s="0" t="n"/>
+      <c r="Y14" s="0" t="n"/>
+      <c r="Z14" s="0" t="n"/>
+      <c r="AA14" s="0" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="0" t="inlineStr">
@@ -2516,6 +2774,16 @@
       <c r="Q15" s="0" t="b">
         <v>0</v>
       </c>
+      <c r="R15" s="0" t="n"/>
+      <c r="S15" s="0" t="n"/>
+      <c r="T15" s="0" t="n"/>
+      <c r="U15" s="0" t="n"/>
+      <c r="V15" s="0" t="n"/>
+      <c r="W15" s="0" t="n"/>
+      <c r="X15" s="0" t="n"/>
+      <c r="Y15" s="0" t="n"/>
+      <c r="Z15" s="0" t="n"/>
+      <c r="AA15" s="0" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="0" t="inlineStr">
@@ -2570,6 +2838,16 @@
       <c r="Q16" s="0" t="b">
         <v>1</v>
       </c>
+      <c r="R16" s="0" t="n"/>
+      <c r="S16" s="0" t="n"/>
+      <c r="T16" s="0" t="n"/>
+      <c r="U16" s="0" t="n"/>
+      <c r="V16" s="0" t="n"/>
+      <c r="W16" s="0" t="n"/>
+      <c r="X16" s="0" t="n"/>
+      <c r="Y16" s="0" t="n"/>
+      <c r="Z16" s="0" t="n"/>
+      <c r="AA16" s="0" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="0" t="inlineStr">
@@ -2624,6 +2902,16 @@
       <c r="Q17" s="0" t="b">
         <v>1</v>
       </c>
+      <c r="R17" s="0" t="n"/>
+      <c r="S17" s="0" t="n"/>
+      <c r="T17" s="0" t="n"/>
+      <c r="U17" s="0" t="n"/>
+      <c r="V17" s="0" t="n"/>
+      <c r="W17" s="0" t="n"/>
+      <c r="X17" s="0" t="n"/>
+      <c r="Y17" s="0" t="n"/>
+      <c r="Z17" s="0" t="n"/>
+      <c r="AA17" s="0" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="0" t="inlineStr">
@@ -2678,9 +2966,73 @@
       <c r="Q18" s="0" t="b">
         <v>0</v>
       </c>
+      <c r="R18" s="0" t="n"/>
+      <c r="S18" s="0" t="n"/>
+      <c r="T18" s="0" t="n"/>
+      <c r="U18" s="0" t="n"/>
+      <c r="V18" s="0" t="n"/>
+      <c r="W18" s="0" t="n"/>
+      <c r="X18" s="0" t="n"/>
+      <c r="Y18" s="0" t="n"/>
+      <c r="Z18" s="0" t="n"/>
+      <c r="AA18" s="0" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>village_01_road</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>晨钟镇南北道</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>晨钟镇南北道</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>village_01_road</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>village_01_road</t>
+        </is>
+      </c>
+      <c r="H19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="0" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2691,7 +3043,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="22.75" customWidth="1" style="1" min="3" max="3"/>
   </cols>
@@ -2892,7 +3244,7 @@
       <c r="I5" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2902,8 +3254,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="14.5" customWidth="1" style="1" min="3" max="3"/>
     <col width="9.5" customWidth="1" style="1" min="4" max="4"/>
@@ -3326,7 +3678,49 @@
         <v>64</v>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>village_01_road</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>village_01_road</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>-16</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="M9" s="0" t="n">
+        <v>240</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Config/Datas/map.xlsx
+++ b/Config/Datas/map.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="logic_area_info" sheetId="1" r:id="Rc7b925aee446499e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="area_variant_info" sheetId="2" r:id="R2114a1d65c934ff2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="area_overlay_state_info" sheetId="3" r:id="R6c612a430aba4d2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="world_map_global" sheetId="4" r:id="R45ce749ed7434699"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="world_map_big_map" sheetId="5" r:id="R33b46e814eec4d2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="logic_area_info" sheetId="1" r:id="R95ea1f51115849da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="area_variant_info" sheetId="2" r:id="R93de1fe2f0ea496f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="area_overlay_state_info" sheetId="3" r:id="R673842c013b14575"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="world_map_global" sheetId="4" r:id="Re872100e13a14ecf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="world_map_big_map" sheetId="5" r:id="R6ad0ce9bc6db40fd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -522,7 +522,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -532,6 +532,17 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
@@ -1674,7 +1685,7 @@
     <x:col min="11" max="11" width="12.625" style="1" customWidth="1"/>
     <x:col min="12" max="12" width="15.125" style="1" customWidth="1"/>
     <x:col min="13" max="13" width="12.625" style="1" customWidth="1"/>
-    <x:col min="14" max="14" width="14.75" style="1" customWidth="1"/>
+    <x:col min="14" max="14" width="28" style="1" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1743,10 +1754,8 @@
           <x:t xml:space="preserve">is_danger_area</x:t>
         </x:is>
       </x:c>
-      <x:c r="N1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">hunting_target</x:t>
-        </x:is>
+      <x:c r="N1" s="4" t="str">
+        <x:v>is_magic_sensitive_area</x:v>
       </x:c>
       <x:c r="O1" t="inlineStr">
         <x:is>
@@ -1880,7 +1889,7 @@
           <x:t xml:space="preserve">bool</x:t>
         </x:is>
       </x:c>
-      <x:c r="N2" t="inlineStr">
+      <x:c r="N2" s="4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">bool</x:t>
         </x:is>
@@ -1997,7 +2006,7 @@
           <x:t xml:space="preserve">c,s</x:t>
         </x:is>
       </x:c>
-      <x:c r="N3" t="inlineStr">
+      <x:c r="N3" s="4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">c,s</x:t>
         </x:is>
@@ -2108,10 +2117,9 @@
 危险区域无法以人形前往</x:t>
         </x:is>
       </x:c>
-      <x:c r="N4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">是否是出击目标</x:t>
-        </x:is>
+      <x:c r="N4" s="4" t="str">
+        <x:v>是否为魔力敏感区
+仅能通过搜打撤/潜入进入，并作为出击目标</x:v>
       </x:c>
       <x:c r="O4" t="inlineStr">
         <x:is>
@@ -2220,7 +2228,7 @@
       <x:c r="M5" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N5" t="b">
+      <x:c r="N5" s="4" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q5" t="b">
@@ -2240,6 +2248,7 @@
     <x:row r="6">
       <x:c r="L6" s="2" t="n"/>
       <x:c r="M6" s="2" t="n"/>
+      <x:c r="N6" s="4"/>
       <x:c r="R6" t="n"/>
       <x:c r="S6" t="n"/>
       <x:c r="T6" t="n"/>
@@ -2295,6 +2304,7 @@
       <x:c r="M7" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N7" s="4"/>
       <x:c r="Q7" t="b">
         <x:v>1</x:v>
       </x:c>
@@ -2344,6 +2354,7 @@
       <x:c r="H8" t="n"/>
       <x:c r="L8" t="n"/>
       <x:c r="M8" t="n"/>
+      <x:c r="N8" s="4"/>
       <x:c r="R8" t="n"/>
       <x:c r="S8" t="n"/>
       <x:c r="T8" t="n"/>
@@ -2399,8 +2410,8 @@
       <x:c r="M9" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N9" t="b">
-        <x:v>1</x:v>
+      <x:c r="N9" s="5" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Q9" t="b">
         <x:v>0</x:v>
@@ -2486,7 +2497,7 @@
       <x:c r="M10" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N10" t="b">
+      <x:c r="N10" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q10" t="b">
@@ -2573,7 +2584,7 @@
       <x:c r="M11" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N11" t="b">
+      <x:c r="N11" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q11" t="b">
@@ -2617,6 +2628,7 @@
       </x:c>
     </x:row>
     <x:row r="12">
+      <x:c r="N12" s="4"/>
       <x:c r="R12" t="n"/>
       <x:c r="S12" t="n"/>
       <x:c r="T12" t="n"/>
@@ -2666,6 +2678,7 @@
       <x:c r="M13" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N13" s="4"/>
       <x:c r="Q13" t="b">
         <x:v>0</x:v>
       </x:c>
@@ -2718,6 +2731,7 @@
       <x:c r="M14" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N14" s="4"/>
       <x:c r="Q14" t="b">
         <x:v>0</x:v>
       </x:c>
@@ -2774,7 +2788,7 @@
       <x:c r="M15" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N15" t="b">
+      <x:c r="N15" s="4" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="P15" t="inlineStr">
@@ -2843,7 +2857,7 @@
       <x:c r="M16" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N16" t="b">
+      <x:c r="N16" s="4" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q16" t="b">
@@ -2907,7 +2921,7 @@
       <x:c r="M17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N17" t="b">
+      <x:c r="N17" s="4" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q17" t="b">
@@ -2971,7 +2985,7 @@
       <x:c r="M18" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N18" t="b">
+      <x:c r="N18" s="5" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q18" t="b">
@@ -3035,7 +3049,7 @@
       <x:c r="M19" s="3" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="N19" t="b">
+      <x:c r="N19" s="4" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q19" s="3" t="b">
